--- a/reports/pdf_rolling5_20260716.xlsx
+++ b/reports/pdf_rolling5_20260716.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="+#,##0;-#,##0;0"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -57,6 +57,10 @@
     <font>
       <b val="1"/>
       <color rgb="000070C0"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
     </font>
     <font>
       <b val="1"/>
@@ -128,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -167,7 +171,8 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -536,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K61"/>
+  <dimension ref="A1:K68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -562,14 +567,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-07-09 ~ 2026-07-16  (최근 5거래일)  ·  캡처 4/7  ·  대기: TIME, TIME, TIGER</t>
+          <t>최근 5거래일 변화  ·  2026-07-09 ~ 2026-07-16  (최근 5거래일)  ·  캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,585억   ·   현금 123억(2.5%)      오늘 2026-07-16  vs  5일전 2026-07-09      매수 20종목  /  매도 18종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,921억   ·   현금 123억(2.5%)      오늘 2026-07-16  vs  5일전 2026-07-09      매수 20종목  /  매도 18종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -665,7 +670,7 @@
         <v>316</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>3159380640</v>
+        <v>3152972160</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -686,7 +691,7 @@
         <v>-78</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-3226290600</v>
+        <v>-3219746400</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -709,7 +714,7 @@
         <v>263</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>4068699420</v>
+        <v>4060446480</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -730,7 +735,7 @@
         <v>-69</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-917778660</v>
+        <v>-915917040</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -753,7 +758,7 @@
         <v>242</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>10498928000</v>
+        <v>10477632000</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -774,7 +779,7 @@
         <v>-61</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1846482200</v>
+        <v>-1842736800</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -797,7 +802,7 @@
         <v>130</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>10241582000</v>
+        <v>10220808000</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -818,7 +823,7 @@
         <v>-54</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-750207960</v>
+        <v>-748686240</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -841,7 +846,7 @@
         <v>80</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>1041216000</v>
+        <v>1039104000</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -862,7 +867,7 @@
         <v>-39</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-1838101200</v>
+        <v>-1834372800</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -885,7 +890,7 @@
         <v>59</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1111705140</v>
+        <v>1109450160</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -906,7 +911,7 @@
         <v>-32</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-809308800</v>
+        <v>-807667200</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -929,7 +934,7 @@
         <v>38</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>2056993200</v>
+        <v>2052820800</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -950,7 +955,7 @@
         <v>-30</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-780912000</v>
+        <v>-779328000</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -973,7 +978,7 @@
         <v>26</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>4004343200</v>
+        <v>3996220800</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -994,7 +999,7 @@
         <v>-22</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-1783082400</v>
+        <v>-1779465600</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1017,7 +1022,7 @@
         <v>24</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>945376800</v>
+        <v>943459200</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1038,7 +1043,7 @@
         <v>-20</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-1335044000</v>
+        <v>-1332336000</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1061,7 +1066,7 @@
         <v>23</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>717758700</v>
+        <v>716302800</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1082,7 +1087,7 @@
         <v>-17</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-3587068000</v>
+        <v>-3579792000</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1105,7 +1110,7 @@
         <v>22</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>916487000</v>
+        <v>914628000</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1126,7 +1131,7 @@
         <v>-15</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-430389000</v>
+        <v>-429516000</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1149,7 +1154,7 @@
         <v>21</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>443108400</v>
+        <v>442209600</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -1170,7 +1175,7 @@
         <v>-13</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-425557600</v>
+        <v>-424694400</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1193,7 +1198,7 @@
         <v>17</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>947053000</v>
+        <v>945132000</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
@@ -1214,7 +1219,7 @@
         <v>-11</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-1738613800</v>
+        <v>-1735087200</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1237,7 +1242,7 @@
         <v>13</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>471061500</v>
+        <v>470106000</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
@@ -1258,7 +1263,7 @@
         <v>-10</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-427924000</v>
+        <v>-427056000</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1281,7 +1286,7 @@
         <v>11</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>966378600</v>
+        <v>964418400</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
@@ -1302,7 +1307,7 @@
         <v>-9</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-372708000</v>
+        <v>-371952000</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1325,7 +1330,7 @@
         <v>10</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>457997000</v>
+        <v>457068000</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
@@ -1346,7 +1351,7 @@
         <v>-7</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-984915400</v>
+        <v>-982917600</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
@@ -1369,7 +1374,7 @@
         <v>8</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>959180800</v>
+        <v>957235200</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
@@ -1390,7 +1395,7 @@
         <v>-6</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-229245000</v>
+        <v>-228780000</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1413,7 +1418,7 @@
         <v>5</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>389470000</v>
+        <v>388680000</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
@@ -1434,7 +1439,7 @@
         <v>-3</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-388089600</v>
+        <v>-387302400</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
@@ -1457,7 +1462,7 @@
         <v>3</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>494281800</v>
+        <v>493279200</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
@@ -1485,7 +1490,7 @@
         <v>3</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>328338000</v>
+        <v>327672000</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
@@ -1506,7 +1511,7 @@
     <row r="27" ht="19" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,024억   ·   현금 23억(0.5%)      오늘 2026-07-16  vs  5일전 2026-07-09      매수 3종목  /  매도 3종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,238억   ·   현금 23억(0.5%)      오늘 2026-07-16  vs  5일전 2026-07-09      매수 3종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B27" s="4" t="n"/>
@@ -1602,7 +1607,7 @@
         <v>83</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>583695840</v>
+        <v>585681200</v>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
@@ -1623,7 +1628,7 @@
         <v>-49</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-880206600</v>
+        <v>-883200500</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
@@ -1646,7 +1651,7 @@
         <v>27</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>1258966800</v>
+        <v>1263249000</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
@@ -1667,7 +1672,7 @@
         <v>-21</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-399457800</v>
+        <v>-400816500</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
@@ -1690,7 +1695,7 @@
         <v>6</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>1017828000</v>
+        <v>1021290000</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
@@ -1711,7 +1716,7 @@
         <v>-12</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>-857304000</v>
+        <v>-860220000</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
@@ -1725,817 +1730,1043 @@
       </c>
     </row>
     <row r="34" ht="19" customHeight="1">
-      <c r="A34" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B34" s="19" t="n"/>
-      <c r="C34" s="19" t="n"/>
-      <c r="D34" s="19" t="n"/>
-      <c r="E34" s="19" t="n"/>
-      <c r="F34" s="19" t="n"/>
-      <c r="G34" s="19" t="n"/>
-      <c r="H34" s="19" t="n"/>
-      <c r="I34" s="19" t="n"/>
-      <c r="J34" s="19" t="n"/>
-      <c r="K34" s="19" t="n"/>
-    </row>
-    <row r="36" ht="19" customHeight="1">
-      <c r="A36" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B36" s="19" t="n"/>
-      <c r="C36" s="19" t="n"/>
-      <c r="D36" s="19" t="n"/>
-      <c r="E36" s="19" t="n"/>
-      <c r="F36" s="19" t="n"/>
-      <c r="G36" s="19" t="n"/>
-      <c r="H36" s="19" t="n"/>
-      <c r="I36" s="19" t="n"/>
-      <c r="J36" s="19" t="n"/>
-      <c r="K36" s="19" t="n"/>
-    </row>
-    <row r="38" ht="19" customHeight="1">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 341억   ·   현금 4억(100.0%)      오늘 2026-07-16  vs  5일전 2026-07-09      매수 9종목  /  매도 14종목</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="n"/>
-      <c r="C38" s="4" t="n"/>
-      <c r="D38" s="4" t="n"/>
-      <c r="E38" s="4" t="n"/>
-      <c r="F38" s="4" t="n"/>
-      <c r="G38" s="4" t="n"/>
-      <c r="H38" s="4" t="n"/>
-      <c r="I38" s="4" t="n"/>
-      <c r="J38" s="4" t="n"/>
-      <c r="K38" s="4" t="n"/>
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,884억   ·   현금 56억(1.9%)      오늘 2026-07-16  vs  5일전 2026-07-09      매수 4종목  /  매도 2종목</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="n"/>
+      <c r="C34" s="4" t="n"/>
+      <c r="D34" s="4" t="n"/>
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="4" t="n"/>
+      <c r="G34" s="4" t="n"/>
+      <c r="H34" s="4" t="n"/>
+      <c r="I34" s="4" t="n"/>
+      <c r="J34" s="4" t="n"/>
+      <c r="K34" s="4" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="6" t="n"/>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="n"/>
+      <c r="I35" s="8" t="n"/>
+      <c r="J35" s="8" t="n"/>
+      <c r="K35" s="8" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G36" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H36" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J36" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K36" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>티엘비</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="n">
+        <v>122</v>
+      </c>
+      <c r="C37" s="11" t="n">
+        <v>3660976000</v>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>2.10%→2.58%</t>
+        </is>
+      </c>
+      <c r="E37" s="13" t="inlineStr">
+        <is>
+          <t>120→242</t>
+        </is>
+      </c>
+      <c r="G37" s="14" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="H37" s="15" t="n">
+        <v>-451</v>
+      </c>
+      <c r="I37" s="15" t="n">
+        <v>-12995339500</v>
+      </c>
+      <c r="J37" s="16" t="inlineStr">
+        <is>
+          <t>8.29%→3.06%</t>
+        </is>
+      </c>
+      <c r="K37" s="13" t="inlineStr">
+        <is>
+          <t>750→299</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>브이엠</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="n">
+        <v>89</v>
+      </c>
+      <c r="C38" s="11" t="n">
+        <v>7034898200</v>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>1.43%→4.21%</t>
+        </is>
+      </c>
+      <c r="E38" s="13" t="inlineStr">
+        <is>
+          <t>61→150</t>
+        </is>
+      </c>
+      <c r="G38" s="14" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="H38" s="15" t="n">
+        <v>-19</v>
+      </c>
+      <c r="I38" s="15" t="n">
+        <v>-3738383000</v>
+      </c>
+      <c r="J38" s="16" t="inlineStr">
+        <is>
+          <t>4.24%→2.10%</t>
+        </is>
+      </c>
+      <c r="K38" s="13" t="inlineStr">
+        <is>
+          <t>49→30</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>주성엔지니어링</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="n">
+        <v>48</v>
+      </c>
+      <c r="C39" s="11" t="n">
+        <v>6858192000</v>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>4.51%→7.61%</t>
+        </is>
+      </c>
+      <c r="E39" s="13" t="inlineStr">
+        <is>
+          <t>102→150</t>
+        </is>
+      </c>
+      <c r="G39" s="17" t="n"/>
+      <c r="H39" s="17" t="n"/>
+      <c r="I39" s="17" t="n"/>
+      <c r="J39" s="17" t="n"/>
+      <c r="K39" s="17" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" s="11" t="n">
+        <v>2918960000</v>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>6.37%→9.85%</t>
+        </is>
+      </c>
+      <c r="E40" s="13" t="inlineStr">
+        <is>
+          <t>170→190</t>
+        </is>
+      </c>
+      <c r="G40" s="17" t="n"/>
+      <c r="H40" s="17" t="n"/>
+      <c r="I40" s="17" t="n"/>
+      <c r="J40" s="17" t="n"/>
+      <c r="K40" s="17" t="n"/>
+    </row>
+    <row r="42" ht="19" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,500억   ·   현금 54억(2.1%)      오늘 2026-07-16  vs  5일전 2026-07-09      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="n"/>
+      <c r="C42" s="4" t="n"/>
+      <c r="D42" s="4" t="n"/>
+      <c r="E42" s="4" t="n"/>
+      <c r="F42" s="4" t="n"/>
+      <c r="G42" s="4" t="n"/>
+      <c r="H42" s="4" t="n"/>
+      <c r="I42" s="4" t="n"/>
+      <c r="J42" s="4" t="n"/>
+      <c r="K42" s="4" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="19" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 359억   ·   현금 4억(100.0%)      오늘 2026-07-16  vs  5일전 2026-07-09      매수 9종목  /  매도 14종목</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="n"/>
+      <c r="C45" s="4" t="n"/>
+      <c r="D45" s="4" t="n"/>
+      <c r="E45" s="4" t="n"/>
+      <c r="F45" s="4" t="n"/>
+      <c r="G45" s="4" t="n"/>
+      <c r="H45" s="4" t="n"/>
+      <c r="I45" s="4" t="n"/>
+      <c r="J45" s="4" t="n"/>
+      <c r="K45" s="4" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B39" s="6" t="n"/>
-      <c r="C39" s="6" t="n"/>
-      <c r="D39" s="6" t="n"/>
-      <c r="E39" s="6" t="n"/>
-      <c r="G39" s="7" t="inlineStr">
+      <c r="B46" s="6" t="n"/>
+      <c r="C46" s="6" t="n"/>
+      <c r="D46" s="6" t="n"/>
+      <c r="E46" s="6" t="n"/>
+      <c r="G46" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H39" s="8" t="n"/>
-      <c r="I39" s="8" t="n"/>
-      <c r="J39" s="8" t="n"/>
-      <c r="K39" s="8" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="9" t="inlineStr">
+      <c r="H46" s="8" t="n"/>
+      <c r="I46" s="8" t="n"/>
+      <c r="J46" s="8" t="n"/>
+      <c r="K46" s="8" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B40" s="9" t="inlineStr">
+      <c r="B47" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C40" s="9" t="inlineStr">
+      <c r="C47" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D40" s="9" t="inlineStr">
+      <c r="D47" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E40" s="9" t="inlineStr">
+      <c r="E47" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G40" s="9" t="inlineStr">
+      <c r="G47" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H40" s="9" t="inlineStr">
+      <c r="H47" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I40" s="9" t="inlineStr">
+      <c r="I47" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J40" s="9" t="inlineStr">
+      <c r="J47" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K40" s="9" t="inlineStr">
+      <c r="K47" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="10" t="inlineStr">
-        <is>
-          <t>더블유씨피</t>
-        </is>
-      </c>
-      <c r="B41" s="11" t="n">
-        <v>198</v>
-      </c>
-      <c r="C41" s="11" t="n">
-        <v>137501100</v>
-      </c>
-      <c r="D41" s="12" t="inlineStr">
-        <is>
-          <t>6.41%→6.84%</t>
-        </is>
-      </c>
-      <c r="E41" s="13" t="inlineStr">
-        <is>
-          <t>3,141→3,339</t>
-        </is>
-      </c>
-      <c r="G41" s="14" t="inlineStr">
-        <is>
-          <t>에이프로</t>
-        </is>
-      </c>
-      <c r="H41" s="15" t="n">
-        <v>-174</v>
-      </c>
-      <c r="I41" s="15" t="n">
-        <v>-40894350</v>
-      </c>
-      <c r="J41" s="16" t="inlineStr">
-        <is>
-          <t>0.41%→0.30%</t>
-        </is>
-      </c>
-      <c r="K41" s="13" t="inlineStr">
-        <is>
-          <t>601→427</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="10" t="inlineStr">
-        <is>
-          <t>씨어스</t>
-        </is>
-      </c>
-      <c r="B42" s="11" t="n">
-        <v>103</v>
-      </c>
-      <c r="C42" s="11" t="n">
-        <v>275782500</v>
-      </c>
-      <c r="D42" s="12" t="inlineStr">
-        <is>
-          <t>5.26%→6.10%</t>
-        </is>
-      </c>
-      <c r="E42" s="13" t="inlineStr">
-        <is>
-          <t>669→772</t>
-        </is>
-      </c>
-      <c r="G42" s="14" t="inlineStr">
-        <is>
-          <t>채비  (편출)</t>
-        </is>
-      </c>
-      <c r="H42" s="15" t="n">
-        <v>-34</v>
-      </c>
-      <c r="I42" s="15" t="n">
-        <v>-15028000</v>
-      </c>
-      <c r="J42" s="16" t="inlineStr">
-        <is>
-          <t>0.04%→0.00%</t>
-        </is>
-      </c>
-      <c r="K42" s="13" t="inlineStr">
-        <is>
-          <t>34→0</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="10" t="inlineStr">
-        <is>
-          <t>서진시스템</t>
-        </is>
-      </c>
-      <c r="B43" s="11" t="n">
-        <v>101</v>
-      </c>
-      <c r="C43" s="11" t="n">
-        <v>323654500</v>
-      </c>
-      <c r="D43" s="12" t="inlineStr">
-        <is>
-          <t>5.92%→6.90%</t>
-        </is>
-      </c>
-      <c r="E43" s="13" t="inlineStr">
-        <is>
-          <t>629→730</t>
-        </is>
-      </c>
-      <c r="G43" s="14" t="inlineStr">
-        <is>
-          <t>액트로</t>
-        </is>
-      </c>
-      <c r="H43" s="15" t="n">
-        <v>-29</v>
-      </c>
-      <c r="I43" s="15" t="n">
-        <v>-18832600</v>
-      </c>
-      <c r="J43" s="16" t="inlineStr">
-        <is>
-          <t>0.35%→0.30%</t>
-        </is>
-      </c>
-      <c r="K43" s="13" t="inlineStr">
-        <is>
-          <t>183→154</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="10" t="inlineStr">
-        <is>
-          <t>에프앤가이드</t>
-        </is>
-      </c>
-      <c r="B44" s="11" t="n">
-        <v>77</v>
-      </c>
-      <c r="C44" s="11" t="n">
-        <v>137772250</v>
-      </c>
-      <c r="D44" s="12" t="inlineStr">
-        <is>
-          <t>2.37%→2.79%</t>
-        </is>
-      </c>
-      <c r="E44" s="13" t="inlineStr">
-        <is>
-          <t>451→528</t>
-        </is>
-      </c>
-      <c r="G44" s="14" t="inlineStr">
-        <is>
-          <t>삼현  (편출)</t>
-        </is>
-      </c>
-      <c r="H44" s="15" t="n">
-        <v>-27</v>
-      </c>
-      <c r="I44" s="15" t="n">
-        <v>-68964750</v>
-      </c>
-      <c r="J44" s="16" t="inlineStr">
-        <is>
-          <t>0.20%→0.00%</t>
-        </is>
-      </c>
-      <c r="K44" s="13" t="inlineStr">
-        <is>
-          <t>27→0</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>인텍플러스</t>
-        </is>
-      </c>
-      <c r="B45" s="11" t="n">
-        <v>74</v>
-      </c>
-      <c r="C45" s="11" t="n">
-        <v>252543500</v>
-      </c>
-      <c r="D45" s="12" t="inlineStr">
-        <is>
-          <t>2.04%→2.80%</t>
-        </is>
-      </c>
-      <c r="E45" s="13" t="inlineStr">
-        <is>
-          <t>204→278</t>
-        </is>
-      </c>
-      <c r="G45" s="14" t="inlineStr">
-        <is>
-          <t>브이엠</t>
-        </is>
-      </c>
-      <c r="H45" s="15" t="n">
-        <v>-27</v>
-      </c>
-      <c r="I45" s="15" t="n">
-        <v>-263236500</v>
-      </c>
-      <c r="J45" s="16" t="inlineStr">
-        <is>
-          <t>4.81%→4.06%</t>
-        </is>
-      </c>
-      <c r="K45" s="13" t="inlineStr">
-        <is>
-          <t>168→141</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="10" t="inlineStr">
-        <is>
-          <t>알멕</t>
-        </is>
-      </c>
-      <c r="B46" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="C46" s="11" t="n">
-        <v>36210000</v>
-      </c>
-      <c r="D46" s="12" t="inlineStr">
-        <is>
-          <t>0.59%→0.70%</t>
-        </is>
-      </c>
-      <c r="E46" s="13" t="inlineStr">
-        <is>
-          <t>83→98</t>
-        </is>
-      </c>
-      <c r="G46" s="14" t="inlineStr">
-        <is>
-          <t>코세스</t>
-        </is>
-      </c>
-      <c r="H46" s="15" t="n">
-        <v>-25</v>
-      </c>
-      <c r="I46" s="15" t="n">
-        <v>-57693750</v>
-      </c>
-      <c r="J46" s="16" t="inlineStr">
-        <is>
-          <t>0.64%→0.48%</t>
-        </is>
-      </c>
-      <c r="K46" s="13" t="inlineStr">
-        <is>
-          <t>95→70</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="10" t="inlineStr">
-        <is>
-          <t>실리콘투</t>
-        </is>
-      </c>
-      <c r="B47" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="C47" s="11" t="n">
-        <v>31025000</v>
-      </c>
-      <c r="D47" s="12" t="inlineStr">
-        <is>
-          <t>0.63%→0.72%</t>
-        </is>
-      </c>
-      <c r="E47" s="13" t="inlineStr">
-        <is>
-          <t>69→79</t>
-        </is>
-      </c>
-      <c r="G47" s="14" t="inlineStr">
-        <is>
-          <t>성호전자</t>
-        </is>
-      </c>
-      <c r="H47" s="15" t="n">
-        <v>-25</v>
-      </c>
-      <c r="I47" s="15" t="n">
-        <v>-39142500</v>
-      </c>
-      <c r="J47" s="16" t="inlineStr">
-        <is>
-          <t>0.40%→0.29%</t>
-        </is>
-      </c>
-      <c r="K47" s="13" t="inlineStr">
-        <is>
-          <t>88→63</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>코스메카코리아  (신규)</t>
+          <t>더블유씨피</t>
         </is>
       </c>
       <c r="B48" s="11" t="n">
-        <v>10</v>
+        <v>198</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>69785000</v>
+        <v>141540300</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.21%</t>
+          <t>6.26%→6.68%</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>0→10</t>
+          <t>3,141→3,339</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>오로스테크놀로지</t>
+          <t>에이프로</t>
         </is>
       </c>
       <c r="H48" s="15" t="n">
-        <v>-22</v>
+        <v>-174</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-33660000</v>
+        <v>-44000250</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>0.38%→0.28%</t>
+          <t>0.42%→0.30%</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
-          <t>85→63</t>
+          <t>601→427</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
+          <t>씨어스</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="n">
+        <v>103</v>
+      </c>
+      <c r="C49" s="11" t="n">
+        <v>283224250</v>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>5.13%→5.95%</t>
+        </is>
+      </c>
+      <c r="E49" s="13" t="inlineStr">
+        <is>
+          <t>669→772</t>
+        </is>
+      </c>
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>채비  (편출)</t>
+        </is>
+      </c>
+      <c r="H49" s="15" t="n">
+        <v>-34</v>
+      </c>
+      <c r="I49" s="15" t="n">
+        <v>-16877600</v>
+      </c>
+      <c r="J49" s="16" t="inlineStr">
+        <is>
+          <t>0.05%→0.00%</t>
+        </is>
+      </c>
+      <c r="K49" s="13" t="inlineStr">
+        <is>
+          <t>34→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>서진시스템</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="n">
+        <v>101</v>
+      </c>
+      <c r="C50" s="11" t="n">
+        <v>360140750</v>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>6.26%→7.29%</t>
+        </is>
+      </c>
+      <c r="E50" s="13" t="inlineStr">
+        <is>
+          <t>629→730</t>
+        </is>
+      </c>
+      <c r="G50" s="14" t="inlineStr">
+        <is>
+          <t>액트로</t>
+        </is>
+      </c>
+      <c r="H50" s="15" t="n">
+        <v>-29</v>
+      </c>
+      <c r="I50" s="15" t="n">
+        <v>-20385550</v>
+      </c>
+      <c r="J50" s="16" t="inlineStr">
+        <is>
+          <t>0.36%→0.30%</t>
+        </is>
+      </c>
+      <c r="K50" s="13" t="inlineStr">
+        <is>
+          <t>183→154</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>에프앤가이드</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="n">
+        <v>77</v>
+      </c>
+      <c r="C51" s="11" t="n">
+        <v>149880500</v>
+      </c>
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>2.45%→2.88%</t>
+        </is>
+      </c>
+      <c r="E51" s="13" t="inlineStr">
+        <is>
+          <t>451→528</t>
+        </is>
+      </c>
+      <c r="G51" s="14" t="inlineStr">
+        <is>
+          <t>브이엠</t>
+        </is>
+      </c>
+      <c r="H51" s="15" t="n">
+        <v>-27</v>
+      </c>
+      <c r="I51" s="15" t="n">
+        <v>-265990500</v>
+      </c>
+      <c r="J51" s="16" t="inlineStr">
+        <is>
+          <t>4.62%→3.89%</t>
+        </is>
+      </c>
+      <c r="K51" s="13" t="inlineStr">
+        <is>
+          <t>168→141</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="n">
+        <v>74</v>
+      </c>
+      <c r="C52" s="11" t="n">
+        <v>265752500</v>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
+        <is>
+          <t>2.04%→2.80%</t>
+        </is>
+      </c>
+      <c r="E52" s="13" t="inlineStr">
+        <is>
+          <t>204→278</t>
+        </is>
+      </c>
+      <c r="G52" s="14" t="inlineStr">
+        <is>
+          <t>삼현  (편출)</t>
+        </is>
+      </c>
+      <c r="H52" s="15" t="n">
+        <v>-27</v>
+      </c>
+      <c r="I52" s="15" t="n">
+        <v>-72292500</v>
+      </c>
+      <c r="J52" s="16" t="inlineStr">
+        <is>
+          <t>0.20%→0.00%</t>
+        </is>
+      </c>
+      <c r="K52" s="13" t="inlineStr">
+        <is>
+          <t>27→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>알멕</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="C53" s="11" t="n">
+        <v>36975000</v>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>0.57%→0.68%</t>
+        </is>
+      </c>
+      <c r="E53" s="13" t="inlineStr">
+        <is>
+          <t>83→98</t>
+        </is>
+      </c>
+      <c r="G53" s="14" t="inlineStr">
+        <is>
+          <t>성호전자</t>
+        </is>
+      </c>
+      <c r="H53" s="15" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I53" s="15" t="n">
+        <v>-42712500</v>
+      </c>
+      <c r="J53" s="16" t="inlineStr">
+        <is>
+          <t>0.42%→0.30%</t>
+        </is>
+      </c>
+      <c r="K53" s="13" t="inlineStr">
+        <is>
+          <t>88→63</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C54" s="11" t="n">
+        <v>31025000</v>
+      </c>
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>0.60%→0.69%</t>
+        </is>
+      </c>
+      <c r="E54" s="13" t="inlineStr">
+        <is>
+          <t>69→79</t>
+        </is>
+      </c>
+      <c r="G54" s="14" t="inlineStr">
+        <is>
+          <t>코세스</t>
+        </is>
+      </c>
+      <c r="H54" s="15" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I54" s="15" t="n">
+        <v>-56100000</v>
+      </c>
+      <c r="J54" s="16" t="inlineStr">
+        <is>
+          <t>0.59%→0.44%</t>
+        </is>
+      </c>
+      <c r="K54" s="13" t="inlineStr">
+        <is>
+          <t>95→70</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>코스메카코리아  (신규)</t>
+        </is>
+      </c>
+      <c r="B55" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C55" s="11" t="n">
+        <v>69785000</v>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.20%</t>
+        </is>
+      </c>
+      <c r="E55" s="13" t="inlineStr">
+        <is>
+          <t>0→10</t>
+        </is>
+      </c>
+      <c r="G55" s="14" t="inlineStr">
+        <is>
+          <t>오로스테크놀로지</t>
+        </is>
+      </c>
+      <c r="H55" s="15" t="n">
+        <v>-22</v>
+      </c>
+      <c r="I55" s="15" t="n">
+        <v>-37194300</v>
+      </c>
+      <c r="J55" s="16" t="inlineStr">
+        <is>
+          <t>0.40%→0.30%</t>
+        </is>
+      </c>
+      <c r="K55" s="13" t="inlineStr">
+        <is>
+          <t>85→63</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
           <t>파두</t>
         </is>
       </c>
-      <c r="B49" s="11" t="n">
+      <c r="B56" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C49" s="11" t="n">
-        <v>36363000</v>
-      </c>
-      <c r="D49" s="12" t="inlineStr">
-        <is>
-          <t>0.87%→0.98%</t>
-        </is>
-      </c>
-      <c r="E49" s="13" t="inlineStr">
+      <c r="C56" s="11" t="n">
+        <v>40749000</v>
+      </c>
+      <c r="D56" s="12" t="inlineStr">
+        <is>
+          <t>0.93%→1.05%</t>
+        </is>
+      </c>
+      <c r="E56" s="13" t="inlineStr">
         <is>
           <t>49→55</t>
         </is>
       </c>
-      <c r="G49" s="14" t="inlineStr">
+      <c r="G56" s="14" t="inlineStr">
         <is>
           <t>테스</t>
         </is>
       </c>
-      <c r="H49" s="15" t="n">
+      <c r="H56" s="15" t="n">
         <v>-21</v>
       </c>
-      <c r="I49" s="15" t="n">
-        <v>-388237500</v>
-      </c>
-      <c r="J49" s="16" t="inlineStr">
-        <is>
-          <t>4.78%→3.66%</t>
-        </is>
-      </c>
-      <c r="K49" s="13" t="inlineStr">
+      <c r="I56" s="15" t="n">
+        <v>-381990000</v>
+      </c>
+      <c r="J56" s="16" t="inlineStr">
+        <is>
+          <t>4.47%→3.41%</t>
+        </is>
+      </c>
+      <c r="K56" s="13" t="inlineStr">
         <is>
           <t>88→67</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="17" t="n"/>
-      <c r="B50" s="17" t="n"/>
-      <c r="C50" s="17" t="n"/>
-      <c r="D50" s="17" t="n"/>
-      <c r="E50" s="17" t="n"/>
-      <c r="G50" s="14" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="17" t="n"/>
+      <c r="B57" s="17" t="n"/>
+      <c r="C57" s="17" t="n"/>
+      <c r="D57" s="17" t="n"/>
+      <c r="E57" s="17" t="n"/>
+      <c r="G57" s="14" t="inlineStr">
         <is>
           <t>피에스케이홀딩스</t>
         </is>
       </c>
-      <c r="H50" s="15" t="n">
+      <c r="H57" s="15" t="n">
         <v>-13</v>
       </c>
-      <c r="I50" s="15" t="n">
-        <v>-155805000</v>
-      </c>
-      <c r="J50" s="16" t="inlineStr">
-        <is>
-          <t>3.52%→3.08%</t>
-        </is>
-      </c>
-      <c r="K50" s="13" t="inlineStr">
+      <c r="I57" s="15" t="n">
+        <v>-172601000</v>
+      </c>
+      <c r="J57" s="16" t="inlineStr">
+        <is>
+          <t>3.70%→3.24%</t>
+        </is>
+      </c>
+      <c r="K57" s="13" t="inlineStr">
         <is>
           <t>100→87</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="17" t="n"/>
-      <c r="B51" s="17" t="n"/>
-      <c r="C51" s="17" t="n"/>
-      <c r="D51" s="17" t="n"/>
-      <c r="E51" s="17" t="n"/>
-      <c r="G51" s="14" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="17" t="n"/>
+      <c r="B58" s="17" t="n"/>
+      <c r="C58" s="17" t="n"/>
+      <c r="D58" s="17" t="n"/>
+      <c r="E58" s="17" t="n"/>
+      <c r="G58" s="14" t="inlineStr">
         <is>
           <t>원익IPS</t>
         </is>
       </c>
-      <c r="H51" s="15" t="n">
+      <c r="H58" s="15" t="n">
         <v>-12</v>
       </c>
-      <c r="I51" s="15" t="n">
-        <v>-129642000</v>
-      </c>
-      <c r="J51" s="16" t="inlineStr">
-        <is>
-          <t>3.08%→2.71%</t>
-        </is>
-      </c>
-      <c r="K51" s="13" t="inlineStr">
+      <c r="I58" s="15" t="n">
+        <v>-145554000</v>
+      </c>
+      <c r="J58" s="16" t="inlineStr">
+        <is>
+          <t>3.28%→2.89%</t>
+        </is>
+      </c>
+      <c r="K58" s="13" t="inlineStr">
         <is>
           <t>97→85</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="17" t="n"/>
-      <c r="B52" s="17" t="n"/>
-      <c r="C52" s="17" t="n"/>
-      <c r="D52" s="17" t="n"/>
-      <c r="E52" s="17" t="n"/>
-      <c r="G52" s="14" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="17" t="n"/>
+      <c r="B59" s="17" t="n"/>
+      <c r="C59" s="17" t="n"/>
+      <c r="D59" s="17" t="n"/>
+      <c r="E59" s="17" t="n"/>
+      <c r="G59" s="14" t="inlineStr">
         <is>
           <t>ISC</t>
         </is>
       </c>
-      <c r="H52" s="15" t="n">
+      <c r="H59" s="15" t="n">
         <v>-7</v>
       </c>
-      <c r="I52" s="15" t="n">
-        <v>-89250000</v>
-      </c>
-      <c r="J52" s="16" t="inlineStr">
-        <is>
-          <t>1.80%→1.54%</t>
-        </is>
-      </c>
-      <c r="K52" s="13" t="inlineStr">
+      <c r="I59" s="15" t="n">
+        <v>-94307500</v>
+      </c>
+      <c r="J59" s="16" t="inlineStr">
+        <is>
+          <t>1.80%→1.55%</t>
+        </is>
+      </c>
+      <c r="K59" s="13" t="inlineStr">
         <is>
           <t>48→41</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="17" t="n"/>
-      <c r="B53" s="17" t="n"/>
-      <c r="C53" s="17" t="n"/>
-      <c r="D53" s="17" t="n"/>
-      <c r="E53" s="17" t="n"/>
-      <c r="G53" s="14" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="17" t="n"/>
+      <c r="B60" s="17" t="n"/>
+      <c r="C60" s="17" t="n"/>
+      <c r="D60" s="17" t="n"/>
+      <c r="E60" s="17" t="n"/>
+      <c r="G60" s="14" t="inlineStr">
         <is>
           <t>기가비스</t>
         </is>
       </c>
-      <c r="H53" s="15" t="n">
+      <c r="H60" s="15" t="n">
         <v>-6</v>
       </c>
-      <c r="I53" s="15" t="n">
-        <v>-79815000</v>
-      </c>
-      <c r="J53" s="16" t="inlineStr">
-        <is>
-          <t>1.64%→1.41%</t>
-        </is>
-      </c>
-      <c r="K53" s="13" t="inlineStr">
+      <c r="I60" s="15" t="n">
+        <v>-85221000</v>
+      </c>
+      <c r="J60" s="16" t="inlineStr">
+        <is>
+          <t>1.66%→1.43%</t>
+        </is>
+      </c>
+      <c r="K60" s="13" t="inlineStr">
         <is>
           <t>42→36</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="17" t="n"/>
-      <c r="B54" s="17" t="n"/>
-      <c r="C54" s="17" t="n"/>
-      <c r="D54" s="17" t="n"/>
-      <c r="E54" s="17" t="n"/>
-      <c r="G54" s="14" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="17" t="n"/>
+      <c r="B61" s="17" t="n"/>
+      <c r="C61" s="17" t="n"/>
+      <c r="D61" s="17" t="n"/>
+      <c r="E61" s="17" t="n"/>
+      <c r="G61" s="14" t="inlineStr">
         <is>
           <t>티씨케이</t>
         </is>
       </c>
-      <c r="H54" s="15" t="n">
+      <c r="H61" s="15" t="n">
         <v>-3</v>
       </c>
-      <c r="I54" s="15" t="n">
-        <v>-60307500</v>
-      </c>
-      <c r="J54" s="16" t="inlineStr">
-        <is>
-          <t>2.78%→2.61%</t>
-        </is>
-      </c>
-      <c r="K54" s="13" t="inlineStr">
+      <c r="I61" s="15" t="n">
+        <v>-57885000</v>
+      </c>
+      <c r="J61" s="16" t="inlineStr">
+        <is>
+          <t>2.53%→2.38%</t>
+        </is>
+      </c>
+      <c r="K61" s="13" t="inlineStr">
         <is>
           <t>47→44</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="19" customHeight="1">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 517억   ·   현금 18억(3.2%)      오늘 2026-07-16  vs  5일전 2026-07-09      매수 1종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="n"/>
-      <c r="C56" s="4" t="n"/>
-      <c r="D56" s="4" t="n"/>
-      <c r="E56" s="4" t="n"/>
-      <c r="F56" s="4" t="n"/>
-      <c r="G56" s="4" t="n"/>
-      <c r="H56" s="4" t="n"/>
-      <c r="I56" s="4" t="n"/>
-      <c r="J56" s="4" t="n"/>
-      <c r="K56" s="4" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
+    <row r="63" ht="19" customHeight="1">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 545억   ·   현금 18억(3.2%)      오늘 2026-07-16  vs  5일전 2026-07-09      매수 1종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="n"/>
+      <c r="C63" s="4" t="n"/>
+      <c r="D63" s="4" t="n"/>
+      <c r="E63" s="4" t="n"/>
+      <c r="F63" s="4" t="n"/>
+      <c r="G63" s="4" t="n"/>
+      <c r="H63" s="4" t="n"/>
+      <c r="I63" s="4" t="n"/>
+      <c r="J63" s="4" t="n"/>
+      <c r="K63" s="4" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B57" s="6" t="n"/>
-      <c r="C57" s="6" t="n"/>
-      <c r="D57" s="6" t="n"/>
-      <c r="E57" s="6" t="n"/>
-      <c r="G57" s="7" t="inlineStr">
+      <c r="B64" s="6" t="n"/>
+      <c r="C64" s="6" t="n"/>
+      <c r="D64" s="6" t="n"/>
+      <c r="E64" s="6" t="n"/>
+      <c r="G64" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H57" s="8" t="n"/>
-      <c r="I57" s="8" t="n"/>
-      <c r="J57" s="8" t="n"/>
-      <c r="K57" s="8" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="9" t="inlineStr">
+      <c r="H64" s="8" t="n"/>
+      <c r="I64" s="8" t="n"/>
+      <c r="J64" s="8" t="n"/>
+      <c r="K64" s="8" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B58" s="9" t="inlineStr">
+      <c r="B65" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C58" s="9" t="inlineStr">
+      <c r="C65" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D58" s="9" t="inlineStr">
+      <c r="D65" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E58" s="9" t="inlineStr">
+      <c r="E65" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G58" s="9" t="inlineStr">
+      <c r="G65" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H58" s="9" t="inlineStr">
+      <c r="H65" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I58" s="9" t="inlineStr">
+      <c r="I65" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J58" s="9" t="inlineStr">
+      <c r="J65" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K58" s="9" t="inlineStr">
+      <c r="K65" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="10" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
         <is>
           <t>큐리오시스</t>
         </is>
       </c>
-      <c r="B59" s="11" t="n">
+      <c r="B66" s="11" t="n">
         <v>296</v>
       </c>
-      <c r="C59" s="11" t="n">
-        <v>534025440</v>
-      </c>
-      <c r="D59" s="12" t="inlineStr">
+      <c r="C66" s="11" t="n">
+        <v>529461120</v>
+      </c>
+      <c r="D66" s="12" t="inlineStr">
         <is>
           <t>1.58%→1.98%</t>
         </is>
       </c>
-      <c r="E59" s="13" t="inlineStr">
+      <c r="E66" s="13" t="inlineStr">
         <is>
           <t>297→593</t>
         </is>
       </c>
-      <c r="G59" s="17" t="n"/>
-      <c r="H59" s="17" t="n"/>
-      <c r="I59" s="17" t="n"/>
-      <c r="J59" s="17" t="n"/>
-      <c r="K59" s="17" t="n"/>
-    </row>
-    <row r="61" ht="19" customHeight="1">
-      <c r="A61" s="18" t="inlineStr">
+      <c r="G66" s="17" t="n"/>
+      <c r="H66" s="17" t="n"/>
+      <c r="I66" s="17" t="n"/>
+      <c r="J66" s="17" t="n"/>
+      <c r="K66" s="17" t="n"/>
+    </row>
+    <row r="68" ht="19" customHeight="1">
+      <c r="A68" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B61" s="19" t="n"/>
-      <c r="C61" s="19" t="n"/>
-      <c r="D61" s="19" t="n"/>
-      <c r="E61" s="19" t="n"/>
-      <c r="F61" s="19" t="n"/>
-      <c r="G61" s="19" t="n"/>
-      <c r="H61" s="19" t="n"/>
-      <c r="I61" s="19" t="n"/>
-      <c r="J61" s="19" t="n"/>
-      <c r="K61" s="19" t="n"/>
+      <c r="B68" s="20" t="n"/>
+      <c r="C68" s="20" t="n"/>
+      <c r="D68" s="20" t="n"/>
+      <c r="E68" s="20" t="n"/>
+      <c r="F68" s="20" t="n"/>
+      <c r="G68" s="20" t="n"/>
+      <c r="H68" s="20" t="n"/>
+      <c r="I68" s="20" t="n"/>
+      <c r="J68" s="20" t="n"/>
+      <c r="K68" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="A61:K61"/>
-    <mergeCell ref="A39:E39"/>
+  <mergeCells count="20">
     <mergeCell ref="A34:K34"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="A45:K45"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="G28:K28"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A27:K27"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A42:K42"/>
+    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="G64:K64"/>
+    <mergeCell ref="A35:E35"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A57:E57"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A27:K27"/>
-    <mergeCell ref="G39:K39"/>
+    <mergeCell ref="G35:K35"/>
     <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A38:K38"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="G28:K28"/>
-    <mergeCell ref="G57:K57"/>
-    <mergeCell ref="A36:K36"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A56:K56"/>
-    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A43:K43"/>
+    <mergeCell ref="A63:K63"/>
+    <mergeCell ref="A68:K68"/>
+    <mergeCell ref="G46:K46"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_rolling5_20260716.xlsx
+++ b/reports/pdf_rolling5_20260716.xlsx
@@ -2231,23 +2231,23 @@
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>삼현  (편출)</t>
         </is>
       </c>
       <c r="H51" s="15" t="n">
         <v>-27</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-265990500</v>
+        <v>-72292500</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>4.62%→3.89%</t>
+          <t>0.20%→0.00%</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
         <is>
-          <t>168→141</t>
+          <t>27→0</t>
         </is>
       </c>
     </row>
@@ -2275,23 +2275,23 @@
       </c>
       <c r="G52" s="14" t="inlineStr">
         <is>
-          <t>삼현  (편출)</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="H52" s="15" t="n">
         <v>-27</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-72292500</v>
+        <v>-265990500</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>0.20%→0.00%</t>
+          <t>4.62%→3.89%</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
-          <t>27→0</t>
+          <t>168→141</t>
         </is>
       </c>
     </row>
@@ -2319,23 +2319,23 @@
       </c>
       <c r="G53" s="14" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="H53" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-42712500</v>
+        <v>-56100000</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>0.42%→0.30%</t>
+          <t>0.59%→0.44%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
-          <t>88→63</t>
+          <t>95→70</t>
         </is>
       </c>
     </row>
@@ -2363,23 +2363,23 @@
       </c>
       <c r="G54" s="14" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="H54" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-56100000</v>
+        <v>-42712500</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>0.59%→0.44%</t>
+          <t>0.42%→0.30%</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
         <is>
-          <t>95→70</t>
+          <t>88→63</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260716.xlsx
+++ b/reports/pdf_rolling5_20260716.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,921억   ·   현금 123억(2.5%)      오늘 2026-07-16  vs  5일전 2026-07-09      매수 20종목  /  매도 18종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      오늘 2026-07-16  vs  5일전 2026-07-09      매수 20종목  /  매도 18종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -669,8 +669,10 @@
       <c r="B6" s="11" t="n">
         <v>316</v>
       </c>
-      <c r="C6" s="11" t="n">
-        <v>3152972160</v>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -690,8 +692,10 @@
       <c r="H6" s="15" t="n">
         <v>-78</v>
       </c>
-      <c r="I6" s="15" t="n">
-        <v>-3219746400</v>
+      <c r="I6" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -713,8 +717,10 @@
       <c r="B7" s="11" t="n">
         <v>263</v>
       </c>
-      <c r="C7" s="11" t="n">
-        <v>4060446480</v>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -734,8 +740,10 @@
       <c r="H7" s="15" t="n">
         <v>-69</v>
       </c>
-      <c r="I7" s="15" t="n">
-        <v>-915917040</v>
+      <c r="I7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -757,8 +765,10 @@
       <c r="B8" s="11" t="n">
         <v>242</v>
       </c>
-      <c r="C8" s="11" t="n">
-        <v>10477632000</v>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -778,8 +788,10 @@
       <c r="H8" s="15" t="n">
         <v>-61</v>
       </c>
-      <c r="I8" s="15" t="n">
-        <v>-1842736800</v>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -801,8 +813,10 @@
       <c r="B9" s="11" t="n">
         <v>130</v>
       </c>
-      <c r="C9" s="11" t="n">
-        <v>10220808000</v>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -822,8 +836,10 @@
       <c r="H9" s="15" t="n">
         <v>-54</v>
       </c>
-      <c r="I9" s="15" t="n">
-        <v>-748686240</v>
+      <c r="I9" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -845,8 +861,10 @@
       <c r="B10" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="C10" s="11" t="n">
-        <v>1039104000</v>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -866,8 +884,10 @@
       <c r="H10" s="15" t="n">
         <v>-39</v>
       </c>
-      <c r="I10" s="15" t="n">
-        <v>-1834372800</v>
+      <c r="I10" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -889,8 +909,10 @@
       <c r="B11" s="11" t="n">
         <v>59</v>
       </c>
-      <c r="C11" s="11" t="n">
-        <v>1109450160</v>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -910,8 +932,10 @@
       <c r="H11" s="15" t="n">
         <v>-32</v>
       </c>
-      <c r="I11" s="15" t="n">
-        <v>-807667200</v>
+      <c r="I11" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -933,8 +957,10 @@
       <c r="B12" s="11" t="n">
         <v>38</v>
       </c>
-      <c r="C12" s="11" t="n">
-        <v>2052820800</v>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -954,8 +980,10 @@
       <c r="H12" s="15" t="n">
         <v>-30</v>
       </c>
-      <c r="I12" s="15" t="n">
-        <v>-779328000</v>
+      <c r="I12" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -977,8 +1005,10 @@
       <c r="B13" s="11" t="n">
         <v>26</v>
       </c>
-      <c r="C13" s="11" t="n">
-        <v>3996220800</v>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -998,8 +1028,10 @@
       <c r="H13" s="15" t="n">
         <v>-22</v>
       </c>
-      <c r="I13" s="15" t="n">
-        <v>-1779465600</v>
+      <c r="I13" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1021,8 +1053,10 @@
       <c r="B14" s="11" t="n">
         <v>24</v>
       </c>
-      <c r="C14" s="11" t="n">
-        <v>943459200</v>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1042,8 +1076,10 @@
       <c r="H14" s="15" t="n">
         <v>-20</v>
       </c>
-      <c r="I14" s="15" t="n">
-        <v>-1332336000</v>
+      <c r="I14" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1065,8 +1101,10 @@
       <c r="B15" s="11" t="n">
         <v>23</v>
       </c>
-      <c r="C15" s="11" t="n">
-        <v>716302800</v>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1086,8 +1124,10 @@
       <c r="H15" s="15" t="n">
         <v>-17</v>
       </c>
-      <c r="I15" s="15" t="n">
-        <v>-3579792000</v>
+      <c r="I15" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1109,8 +1149,10 @@
       <c r="B16" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="C16" s="11" t="n">
-        <v>914628000</v>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1130,8 +1172,10 @@
       <c r="H16" s="15" t="n">
         <v>-15</v>
       </c>
-      <c r="I16" s="15" t="n">
-        <v>-429516000</v>
+      <c r="I16" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1153,8 +1197,10 @@
       <c r="B17" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="C17" s="11" t="n">
-        <v>442209600</v>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -1174,8 +1220,10 @@
       <c r="H17" s="15" t="n">
         <v>-13</v>
       </c>
-      <c r="I17" s="15" t="n">
-        <v>-424694400</v>
+      <c r="I17" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1197,8 +1245,10 @@
       <c r="B18" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="C18" s="11" t="n">
-        <v>945132000</v>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
@@ -1218,8 +1268,10 @@
       <c r="H18" s="15" t="n">
         <v>-11</v>
       </c>
-      <c r="I18" s="15" t="n">
-        <v>-1735087200</v>
+      <c r="I18" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1241,8 +1293,10 @@
       <c r="B19" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="C19" s="11" t="n">
-        <v>470106000</v>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
@@ -1262,8 +1316,10 @@
       <c r="H19" s="15" t="n">
         <v>-10</v>
       </c>
-      <c r="I19" s="15" t="n">
-        <v>-427056000</v>
+      <c r="I19" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1285,8 +1341,10 @@
       <c r="B20" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="C20" s="11" t="n">
-        <v>964418400</v>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
@@ -1306,8 +1364,10 @@
       <c r="H20" s="15" t="n">
         <v>-9</v>
       </c>
-      <c r="I20" s="15" t="n">
-        <v>-371952000</v>
+      <c r="I20" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1329,8 +1389,10 @@
       <c r="B21" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="C21" s="11" t="n">
-        <v>457068000</v>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
@@ -1350,8 +1412,10 @@
       <c r="H21" s="15" t="n">
         <v>-7</v>
       </c>
-      <c r="I21" s="15" t="n">
-        <v>-982917600</v>
+      <c r="I21" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
@@ -1373,8 +1437,10 @@
       <c r="B22" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="C22" s="11" t="n">
-        <v>957235200</v>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
@@ -1394,8 +1460,10 @@
       <c r="H22" s="15" t="n">
         <v>-6</v>
       </c>
-      <c r="I22" s="15" t="n">
-        <v>-228780000</v>
+      <c r="I22" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1417,8 +1485,10 @@
       <c r="B23" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C23" s="11" t="n">
-        <v>388680000</v>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
@@ -1438,8 +1508,10 @@
       <c r="H23" s="15" t="n">
         <v>-3</v>
       </c>
-      <c r="I23" s="15" t="n">
-        <v>-387302400</v>
+      <c r="I23" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
@@ -1455,23 +1527,25 @@
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="B24" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C24" s="11" t="n">
-        <v>493279200</v>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>1.26%→1.33%</t>
+          <t>2.15%→1.74%</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>36→39</t>
+          <t>74→77</t>
         </is>
       </c>
       <c r="G24" s="17" t="n"/>
@@ -1483,23 +1557,25 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="B25" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C25" s="11" t="n">
-        <v>327672000</v>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>2.15%→1.74%</t>
+          <t>1.26%→1.33%</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>74→77</t>
+          <t>36→39</t>
         </is>
       </c>
       <c r="G25" s="17" t="n"/>
@@ -1511,7 +1587,7 @@
     <row r="27" ht="19" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,238억   ·   현금 23억(0.5%)      오늘 2026-07-16  vs  5일전 2026-07-09      매수 3종목  /  매도 3종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      오늘 2026-07-16  vs  5일전 2026-07-09      매수 3종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B27" s="4" t="n"/>
@@ -1606,8 +1682,10 @@
       <c r="B30" s="11" t="n">
         <v>83</v>
       </c>
-      <c r="C30" s="11" t="n">
-        <v>585681200</v>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
@@ -1627,8 +1705,10 @@
       <c r="H30" s="15" t="n">
         <v>-49</v>
       </c>
-      <c r="I30" s="15" t="n">
-        <v>-883200500</v>
+      <c r="I30" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
@@ -1650,8 +1730,10 @@
       <c r="B31" s="11" t="n">
         <v>27</v>
       </c>
-      <c r="C31" s="11" t="n">
-        <v>1263249000</v>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
@@ -1671,8 +1753,10 @@
       <c r="H31" s="15" t="n">
         <v>-21</v>
       </c>
-      <c r="I31" s="15" t="n">
-        <v>-400816500</v>
+      <c r="I31" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
@@ -1694,8 +1778,10 @@
       <c r="B32" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C32" s="11" t="n">
-        <v>1021290000</v>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
@@ -1715,8 +1801,10 @@
       <c r="H32" s="15" t="n">
         <v>-12</v>
       </c>
-      <c r="I32" s="15" t="n">
-        <v>-860220000</v>
+      <c r="I32" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
@@ -1732,7 +1820,7 @@
     <row r="34" ht="19" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,884억   ·   현금 56억(1.9%)      오늘 2026-07-16  vs  5일전 2026-07-09      매수 4종목  /  매도 2종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      오늘 2026-07-16  vs  5일전 2026-07-09      매수 4종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B34" s="4" t="n"/>
@@ -1827,8 +1915,10 @@
       <c r="B37" s="11" t="n">
         <v>122</v>
       </c>
-      <c r="C37" s="11" t="n">
-        <v>3660976000</v>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
@@ -1848,8 +1938,10 @@
       <c r="H37" s="15" t="n">
         <v>-451</v>
       </c>
-      <c r="I37" s="15" t="n">
-        <v>-12995339500</v>
+      <c r="I37" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
@@ -1871,8 +1963,10 @@
       <c r="B38" s="11" t="n">
         <v>89</v>
       </c>
-      <c r="C38" s="11" t="n">
-        <v>7034898200</v>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
@@ -1892,8 +1986,10 @@
       <c r="H38" s="15" t="n">
         <v>-19</v>
       </c>
-      <c r="I38" s="15" t="n">
-        <v>-3738383000</v>
+      <c r="I38" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
@@ -1915,8 +2011,10 @@
       <c r="B39" s="11" t="n">
         <v>48</v>
       </c>
-      <c r="C39" s="11" t="n">
-        <v>6858192000</v>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
@@ -1943,8 +2041,10 @@
       <c r="B40" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="C40" s="11" t="n">
-        <v>2918960000</v>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
@@ -1965,7 +2065,7 @@
     <row r="42" ht="19" customHeight="1">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,500억   ·   현금 54억(2.1%)      오늘 2026-07-16  vs  5일전 2026-07-09      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      오늘 2026-07-16  vs  5일전 2026-07-09      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B42" s="4" t="n"/>
@@ -1989,7 +2089,7 @@
     <row r="45" ht="19" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 359억   ·   현금 4억(100.0%)      오늘 2026-07-16  vs  5일전 2026-07-09      매수 9종목  /  매도 14종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      오늘 2026-07-16  vs  5일전 2026-07-09      매수 9종목  /  매도 14종목</t>
         </is>
       </c>
       <c r="B45" s="4" t="n"/>
@@ -2084,12 +2184,14 @@
       <c r="B48" s="11" t="n">
         <v>198</v>
       </c>
-      <c r="C48" s="11" t="n">
-        <v>141540300</v>
+      <c r="C48" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>6.26%→6.68%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
@@ -2105,12 +2207,14 @@
       <c r="H48" s="15" t="n">
         <v>-174</v>
       </c>
-      <c r="I48" s="15" t="n">
-        <v>-44000250</v>
+      <c r="I48" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>0.42%→0.30%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
@@ -2128,12 +2232,14 @@
       <c r="B49" s="11" t="n">
         <v>103</v>
       </c>
-      <c r="C49" s="11" t="n">
-        <v>283224250</v>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>5.13%→5.95%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
@@ -2149,12 +2255,14 @@
       <c r="H49" s="15" t="n">
         <v>-34</v>
       </c>
-      <c r="I49" s="15" t="n">
-        <v>-16877600</v>
+      <c r="I49" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>0.05%→0.00%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
@@ -2172,12 +2280,14 @@
       <c r="B50" s="11" t="n">
         <v>101</v>
       </c>
-      <c r="C50" s="11" t="n">
-        <v>360140750</v>
+      <c r="C50" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>6.26%→7.29%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
@@ -2193,12 +2303,14 @@
       <c r="H50" s="15" t="n">
         <v>-29</v>
       </c>
-      <c r="I50" s="15" t="n">
-        <v>-20385550</v>
+      <c r="I50" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>0.36%→0.30%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
@@ -2216,12 +2328,14 @@
       <c r="B51" s="11" t="n">
         <v>77</v>
       </c>
-      <c r="C51" s="11" t="n">
-        <v>149880500</v>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>2.45%→2.88%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
@@ -2237,12 +2351,14 @@
       <c r="H51" s="15" t="n">
         <v>-27</v>
       </c>
-      <c r="I51" s="15" t="n">
-        <v>-72292500</v>
+      <c r="I51" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>0.20%→0.00%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
@@ -2260,12 +2376,14 @@
       <c r="B52" s="11" t="n">
         <v>74</v>
       </c>
-      <c r="C52" s="11" t="n">
-        <v>265752500</v>
+      <c r="C52" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>2.04%→2.80%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
@@ -2281,12 +2399,14 @@
       <c r="H52" s="15" t="n">
         <v>-27</v>
       </c>
-      <c r="I52" s="15" t="n">
-        <v>-265990500</v>
+      <c r="I52" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>4.62%→3.89%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
@@ -2304,12 +2424,14 @@
       <c r="B53" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="C53" s="11" t="n">
-        <v>36975000</v>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>0.57%→0.68%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
@@ -2325,12 +2447,14 @@
       <c r="H53" s="15" t="n">
         <v>-25</v>
       </c>
-      <c r="I53" s="15" t="n">
-        <v>-56100000</v>
+      <c r="I53" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>0.59%→0.44%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
@@ -2348,12 +2472,14 @@
       <c r="B54" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="C54" s="11" t="n">
-        <v>31025000</v>
+      <c r="C54" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>0.60%→0.69%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
@@ -2369,12 +2495,14 @@
       <c r="H54" s="15" t="n">
         <v>-25</v>
       </c>
-      <c r="I54" s="15" t="n">
-        <v>-42712500</v>
+      <c r="I54" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>0.42%→0.30%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
@@ -2392,12 +2520,14 @@
       <c r="B55" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="C55" s="11" t="n">
-        <v>69785000</v>
+      <c r="C55" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.20%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
@@ -2413,12 +2543,14 @@
       <c r="H55" s="15" t="n">
         <v>-22</v>
       </c>
-      <c r="I55" s="15" t="n">
-        <v>-37194300</v>
+      <c r="I55" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>0.40%→0.30%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
@@ -2436,12 +2568,14 @@
       <c r="B56" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C56" s="11" t="n">
-        <v>40749000</v>
+      <c r="C56" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>0.93%→1.05%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
@@ -2457,12 +2591,14 @@
       <c r="H56" s="15" t="n">
         <v>-21</v>
       </c>
-      <c r="I56" s="15" t="n">
-        <v>-381990000</v>
+      <c r="I56" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>4.47%→3.41%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
@@ -2485,12 +2621,14 @@
       <c r="H57" s="15" t="n">
         <v>-13</v>
       </c>
-      <c r="I57" s="15" t="n">
-        <v>-172601000</v>
+      <c r="I57" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>3.70%→3.24%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
@@ -2513,12 +2651,14 @@
       <c r="H58" s="15" t="n">
         <v>-12</v>
       </c>
-      <c r="I58" s="15" t="n">
-        <v>-145554000</v>
+      <c r="I58" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>3.28%→2.89%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
@@ -2541,12 +2681,14 @@
       <c r="H59" s="15" t="n">
         <v>-7</v>
       </c>
-      <c r="I59" s="15" t="n">
-        <v>-94307500</v>
+      <c r="I59" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>1.80%→1.55%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
@@ -2569,12 +2711,14 @@
       <c r="H60" s="15" t="n">
         <v>-6</v>
       </c>
-      <c r="I60" s="15" t="n">
-        <v>-85221000</v>
+      <c r="I60" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
-          <t>1.66%→1.43%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="13" t="inlineStr">
@@ -2597,12 +2741,14 @@
       <c r="H61" s="15" t="n">
         <v>-3</v>
       </c>
-      <c r="I61" s="15" t="n">
-        <v>-57885000</v>
+      <c r="I61" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>2.53%→2.38%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K61" s="13" t="inlineStr">
@@ -2614,7 +2760,7 @@
     <row r="63" ht="19" customHeight="1">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 545억   ·   현금 18억(3.2%)      오늘 2026-07-16  vs  5일전 2026-07-09      매수 1종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      오늘 2026-07-16  vs  5일전 2026-07-09      매수 1종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B63" s="4" t="n"/>
@@ -2709,8 +2855,10 @@
       <c r="B66" s="11" t="n">
         <v>296</v>
       </c>
-      <c r="C66" s="11" t="n">
-        <v>529461120</v>
+      <c r="C66" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>

--- a/reports/pdf_rolling5_20260716.xlsx
+++ b/reports/pdf_rolling5_20260716.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      오늘 2026-07-16  vs  5일전 2026-07-09      매수 20종목  /  매도 18종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,921억   ·   현금 123억(2.5%)      오늘 2026-07-16  vs  5일전 2026-07-09      매수 20종목  /  매도 18종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -669,10 +669,8 @@
       <c r="B6" s="11" t="n">
         <v>316</v>
       </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C6" s="11" t="n">
+        <v>3152972160</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -692,10 +690,8 @@
       <c r="H6" s="15" t="n">
         <v>-78</v>
       </c>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I6" s="15" t="n">
+        <v>-3219746400</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -717,10 +713,8 @@
       <c r="B7" s="11" t="n">
         <v>263</v>
       </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C7" s="11" t="n">
+        <v>4060446480</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -740,10 +734,8 @@
       <c r="H7" s="15" t="n">
         <v>-69</v>
       </c>
-      <c r="I7" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I7" s="15" t="n">
+        <v>-915917040</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -765,10 +757,8 @@
       <c r="B8" s="11" t="n">
         <v>242</v>
       </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C8" s="11" t="n">
+        <v>10477632000</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -788,10 +778,8 @@
       <c r="H8" s="15" t="n">
         <v>-61</v>
       </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I8" s="15" t="n">
+        <v>-1842736800</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -813,10 +801,8 @@
       <c r="B9" s="11" t="n">
         <v>130</v>
       </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C9" s="11" t="n">
+        <v>10220808000</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -836,10 +822,8 @@
       <c r="H9" s="15" t="n">
         <v>-54</v>
       </c>
-      <c r="I9" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I9" s="15" t="n">
+        <v>-748686240</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -861,10 +845,8 @@
       <c r="B10" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C10" s="11" t="n">
+        <v>1039104000</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -884,10 +866,8 @@
       <c r="H10" s="15" t="n">
         <v>-39</v>
       </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I10" s="15" t="n">
+        <v>-1834372800</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -909,10 +889,8 @@
       <c r="B11" s="11" t="n">
         <v>59</v>
       </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C11" s="11" t="n">
+        <v>1109450160</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -932,10 +910,8 @@
       <c r="H11" s="15" t="n">
         <v>-32</v>
       </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I11" s="15" t="n">
+        <v>-807667200</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -957,10 +933,8 @@
       <c r="B12" s="11" t="n">
         <v>38</v>
       </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C12" s="11" t="n">
+        <v>2052820800</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -980,10 +954,8 @@
       <c r="H12" s="15" t="n">
         <v>-30</v>
       </c>
-      <c r="I12" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I12" s="15" t="n">
+        <v>-779328000</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -1005,10 +977,8 @@
       <c r="B13" s="11" t="n">
         <v>26</v>
       </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C13" s="11" t="n">
+        <v>3996220800</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -1028,10 +998,8 @@
       <c r="H13" s="15" t="n">
         <v>-22</v>
       </c>
-      <c r="I13" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I13" s="15" t="n">
+        <v>-1779465600</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1053,10 +1021,8 @@
       <c r="B14" s="11" t="n">
         <v>24</v>
       </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C14" s="11" t="n">
+        <v>943459200</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1076,10 +1042,8 @@
       <c r="H14" s="15" t="n">
         <v>-20</v>
       </c>
-      <c r="I14" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I14" s="15" t="n">
+        <v>-1332336000</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1101,10 +1065,8 @@
       <c r="B15" s="11" t="n">
         <v>23</v>
       </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C15" s="11" t="n">
+        <v>716302800</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1124,10 +1086,8 @@
       <c r="H15" s="15" t="n">
         <v>-17</v>
       </c>
-      <c r="I15" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I15" s="15" t="n">
+        <v>-3579792000</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1149,10 +1109,8 @@
       <c r="B16" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="C16" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C16" s="11" t="n">
+        <v>914628000</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1172,10 +1130,8 @@
       <c r="H16" s="15" t="n">
         <v>-15</v>
       </c>
-      <c r="I16" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I16" s="15" t="n">
+        <v>-429516000</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1197,10 +1153,8 @@
       <c r="B17" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C17" s="11" t="n">
+        <v>442209600</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -1220,10 +1174,8 @@
       <c r="H17" s="15" t="n">
         <v>-13</v>
       </c>
-      <c r="I17" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I17" s="15" t="n">
+        <v>-424694400</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1245,10 +1197,8 @@
       <c r="B18" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="C18" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C18" s="11" t="n">
+        <v>945132000</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
@@ -1268,10 +1218,8 @@
       <c r="H18" s="15" t="n">
         <v>-11</v>
       </c>
-      <c r="I18" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I18" s="15" t="n">
+        <v>-1735087200</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1293,10 +1241,8 @@
       <c r="B19" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C19" s="11" t="n">
+        <v>470106000</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
@@ -1316,10 +1262,8 @@
       <c r="H19" s="15" t="n">
         <v>-10</v>
       </c>
-      <c r="I19" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I19" s="15" t="n">
+        <v>-427056000</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1341,10 +1285,8 @@
       <c r="B20" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="C20" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C20" s="11" t="n">
+        <v>964418400</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
@@ -1364,10 +1306,8 @@
       <c r="H20" s="15" t="n">
         <v>-9</v>
       </c>
-      <c r="I20" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I20" s="15" t="n">
+        <v>-371952000</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1389,10 +1329,8 @@
       <c r="B21" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C21" s="11" t="n">
+        <v>457068000</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
@@ -1412,10 +1350,8 @@
       <c r="H21" s="15" t="n">
         <v>-7</v>
       </c>
-      <c r="I21" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I21" s="15" t="n">
+        <v>-982917600</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
@@ -1437,10 +1373,8 @@
       <c r="B22" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C22" s="11" t="n">
+        <v>957235200</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
@@ -1460,10 +1394,8 @@
       <c r="H22" s="15" t="n">
         <v>-6</v>
       </c>
-      <c r="I22" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I22" s="15" t="n">
+        <v>-228780000</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1485,10 +1417,8 @@
       <c r="B23" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C23" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C23" s="11" t="n">
+        <v>388680000</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
@@ -1508,10 +1438,8 @@
       <c r="H23" s="15" t="n">
         <v>-3</v>
       </c>
-      <c r="I23" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I23" s="15" t="n">
+        <v>-387302400</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
@@ -1527,25 +1455,23 @@
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="B24" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C24" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C24" s="11" t="n">
+        <v>493279200</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>2.15%→1.74%</t>
+          <t>1.26%→1.33%</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>74→77</t>
+          <t>36→39</t>
         </is>
       </c>
       <c r="G24" s="17" t="n"/>
@@ -1557,25 +1483,23 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="B25" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C25" s="11" t="n">
+        <v>327672000</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>1.26%→1.33%</t>
+          <t>2.15%→1.74%</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>36→39</t>
+          <t>74→77</t>
         </is>
       </c>
       <c r="G25" s="17" t="n"/>
@@ -1587,7 +1511,7 @@
     <row r="27" ht="19" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      오늘 2026-07-16  vs  5일전 2026-07-09      매수 3종목  /  매도 3종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,238억   ·   현금 23억(0.5%)      오늘 2026-07-16  vs  5일전 2026-07-09      매수 3종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B27" s="4" t="n"/>
@@ -1682,10 +1606,8 @@
       <c r="B30" s="11" t="n">
         <v>83</v>
       </c>
-      <c r="C30" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C30" s="11" t="n">
+        <v>585681200</v>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
@@ -1705,10 +1627,8 @@
       <c r="H30" s="15" t="n">
         <v>-49</v>
       </c>
-      <c r="I30" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I30" s="15" t="n">
+        <v>-883200500</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
@@ -1730,10 +1650,8 @@
       <c r="B31" s="11" t="n">
         <v>27</v>
       </c>
-      <c r="C31" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C31" s="11" t="n">
+        <v>1263249000</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
@@ -1753,10 +1671,8 @@
       <c r="H31" s="15" t="n">
         <v>-21</v>
       </c>
-      <c r="I31" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I31" s="15" t="n">
+        <v>-400816500</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
@@ -1778,10 +1694,8 @@
       <c r="B32" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C32" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C32" s="11" t="n">
+        <v>1021290000</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
@@ -1801,10 +1715,8 @@
       <c r="H32" s="15" t="n">
         <v>-12</v>
       </c>
-      <c r="I32" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I32" s="15" t="n">
+        <v>-860220000</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
@@ -1820,7 +1732,7 @@
     <row r="34" ht="19" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      오늘 2026-07-16  vs  5일전 2026-07-09      매수 4종목  /  매도 2종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,884억   ·   현금 56억(1.9%)      오늘 2026-07-16  vs  5일전 2026-07-09      매수 4종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B34" s="4" t="n"/>
@@ -1915,10 +1827,8 @@
       <c r="B37" s="11" t="n">
         <v>122</v>
       </c>
-      <c r="C37" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C37" s="11" t="n">
+        <v>3660976000</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
@@ -1938,10 +1848,8 @@
       <c r="H37" s="15" t="n">
         <v>-451</v>
       </c>
-      <c r="I37" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I37" s="15" t="n">
+        <v>-12995339500</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
@@ -1963,10 +1871,8 @@
       <c r="B38" s="11" t="n">
         <v>89</v>
       </c>
-      <c r="C38" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C38" s="11" t="n">
+        <v>7034898200</v>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
@@ -1986,10 +1892,8 @@
       <c r="H38" s="15" t="n">
         <v>-19</v>
       </c>
-      <c r="I38" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I38" s="15" t="n">
+        <v>-3738383000</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
@@ -2011,10 +1915,8 @@
       <c r="B39" s="11" t="n">
         <v>48</v>
       </c>
-      <c r="C39" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C39" s="11" t="n">
+        <v>6858192000</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
@@ -2041,10 +1943,8 @@
       <c r="B40" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="C40" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C40" s="11" t="n">
+        <v>2918960000</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
@@ -2065,7 +1965,7 @@
     <row r="42" ht="19" customHeight="1">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      오늘 2026-07-16  vs  5일전 2026-07-09      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,500억   ·   현금 54억(2.1%)      오늘 2026-07-16  vs  5일전 2026-07-09      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B42" s="4" t="n"/>
@@ -2089,7 +1989,7 @@
     <row r="45" ht="19" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      오늘 2026-07-16  vs  5일전 2026-07-09      매수 9종목  /  매도 14종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 359억   ·   현금 4억(100.0%)      오늘 2026-07-16  vs  5일전 2026-07-09      매수 9종목  /  매도 14종목</t>
         </is>
       </c>
       <c r="B45" s="4" t="n"/>
@@ -2184,14 +2084,12 @@
       <c r="B48" s="11" t="n">
         <v>198</v>
       </c>
-      <c r="C48" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C48" s="11" t="n">
+        <v>141540300</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6.26%→6.68%</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
@@ -2207,14 +2105,12 @@
       <c r="H48" s="15" t="n">
         <v>-174</v>
       </c>
-      <c r="I48" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I48" s="15" t="n">
+        <v>-44000250</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.42%→0.30%</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
@@ -2232,14 +2128,12 @@
       <c r="B49" s="11" t="n">
         <v>103</v>
       </c>
-      <c r="C49" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C49" s="11" t="n">
+        <v>283224250</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5.13%→5.95%</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
@@ -2255,14 +2149,12 @@
       <c r="H49" s="15" t="n">
         <v>-34</v>
       </c>
-      <c r="I49" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I49" s="15" t="n">
+        <v>-16877600</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.05%→0.00%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
@@ -2280,14 +2172,12 @@
       <c r="B50" s="11" t="n">
         <v>101</v>
       </c>
-      <c r="C50" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C50" s="11" t="n">
+        <v>360140750</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6.26%→7.29%</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
@@ -2303,14 +2193,12 @@
       <c r="H50" s="15" t="n">
         <v>-29</v>
       </c>
-      <c r="I50" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I50" s="15" t="n">
+        <v>-20385550</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.36%→0.30%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
@@ -2328,14 +2216,12 @@
       <c r="B51" s="11" t="n">
         <v>77</v>
       </c>
-      <c r="C51" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C51" s="11" t="n">
+        <v>149880500</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.45%→2.88%</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
@@ -2351,14 +2237,12 @@
       <c r="H51" s="15" t="n">
         <v>-27</v>
       </c>
-      <c r="I51" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I51" s="15" t="n">
+        <v>-72292500</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.20%→0.00%</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
@@ -2376,14 +2260,12 @@
       <c r="B52" s="11" t="n">
         <v>74</v>
       </c>
-      <c r="C52" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C52" s="11" t="n">
+        <v>265752500</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.04%→2.80%</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
@@ -2399,14 +2281,12 @@
       <c r="H52" s="15" t="n">
         <v>-27</v>
       </c>
-      <c r="I52" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I52" s="15" t="n">
+        <v>-265990500</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4.62%→3.89%</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
@@ -2424,14 +2304,12 @@
       <c r="B53" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="C53" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C53" s="11" t="n">
+        <v>36975000</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.57%→0.68%</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
@@ -2447,14 +2325,12 @@
       <c r="H53" s="15" t="n">
         <v>-25</v>
       </c>
-      <c r="I53" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I53" s="15" t="n">
+        <v>-56100000</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.59%→0.44%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
@@ -2466,25 +2342,23 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>코스메카코리아  (신규)</t>
         </is>
       </c>
       <c r="B54" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="C54" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C54" s="11" t="n">
+        <v>69785000</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.00%→0.20%</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>69→79</t>
+          <t>0→10</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
@@ -2495,14 +2369,12 @@
       <c r="H54" s="15" t="n">
         <v>-25</v>
       </c>
-      <c r="I54" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I54" s="15" t="n">
+        <v>-42712500</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.42%→0.30%</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
@@ -2514,25 +2386,23 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>코스메카코리아  (신규)</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="B55" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="C55" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C55" s="11" t="n">
+        <v>31025000</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.60%→0.69%</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
-          <t>0→10</t>
+          <t>69→79</t>
         </is>
       </c>
       <c r="G55" s="14" t="inlineStr">
@@ -2543,14 +2413,12 @@
       <c r="H55" s="15" t="n">
         <v>-22</v>
       </c>
-      <c r="I55" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I55" s="15" t="n">
+        <v>-37194300</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.40%→0.30%</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
@@ -2568,14 +2436,12 @@
       <c r="B56" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C56" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C56" s="11" t="n">
+        <v>40749000</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.93%→1.05%</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
@@ -2591,14 +2457,12 @@
       <c r="H56" s="15" t="n">
         <v>-21</v>
       </c>
-      <c r="I56" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I56" s="15" t="n">
+        <v>-381990000</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4.47%→3.41%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
@@ -2621,14 +2485,12 @@
       <c r="H57" s="15" t="n">
         <v>-13</v>
       </c>
-      <c r="I57" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I57" s="15" t="n">
+        <v>-172601000</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.70%→3.24%</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
@@ -2651,14 +2513,12 @@
       <c r="H58" s="15" t="n">
         <v>-12</v>
       </c>
-      <c r="I58" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I58" s="15" t="n">
+        <v>-145554000</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.28%→2.89%</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
@@ -2681,14 +2541,12 @@
       <c r="H59" s="15" t="n">
         <v>-7</v>
       </c>
-      <c r="I59" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I59" s="15" t="n">
+        <v>-94307500</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.80%→1.55%</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
@@ -2711,14 +2569,12 @@
       <c r="H60" s="15" t="n">
         <v>-6</v>
       </c>
-      <c r="I60" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I60" s="15" t="n">
+        <v>-85221000</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.66%→1.43%</t>
         </is>
       </c>
       <c r="K60" s="13" t="inlineStr">
@@ -2741,14 +2597,12 @@
       <c r="H61" s="15" t="n">
         <v>-3</v>
       </c>
-      <c r="I61" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I61" s="15" t="n">
+        <v>-57885000</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.53%→2.38%</t>
         </is>
       </c>
       <c r="K61" s="13" t="inlineStr">
@@ -2760,7 +2614,7 @@
     <row r="63" ht="19" customHeight="1">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      오늘 2026-07-16  vs  5일전 2026-07-09      매수 1종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 545억   ·   현금 18억(3.2%)      오늘 2026-07-16  vs  5일전 2026-07-09      매수 1종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B63" s="4" t="n"/>
@@ -2855,10 +2709,8 @@
       <c r="B66" s="11" t="n">
         <v>296</v>
       </c>
-      <c r="C66" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C66" s="11" t="n">
+        <v>529461120</v>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>

--- a/reports/pdf_rolling5_20260716.xlsx
+++ b/reports/pdf_rolling5_20260716.xlsx
@@ -1455,23 +1455,23 @@
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="B24" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>493279200</v>
+        <v>327672000</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>1.26%→1.33%</t>
+          <t>2.15%→1.74%</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>36→39</t>
+          <t>74→77</t>
         </is>
       </c>
       <c r="G24" s="17" t="n"/>
@@ -1483,23 +1483,23 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="B25" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>327672000</v>
+        <v>493279200</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>2.15%→1.74%</t>
+          <t>1.26%→1.33%</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>74→77</t>
+          <t>36→39</t>
         </is>
       </c>
       <c r="G25" s="17" t="n"/>
@@ -2231,23 +2231,23 @@
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>
-          <t>삼현  (편출)</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="H51" s="15" t="n">
         <v>-27</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-72292500</v>
+        <v>-265990500</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>0.20%→0.00%</t>
+          <t>4.62%→3.89%</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
         <is>
-          <t>27→0</t>
+          <t>168→141</t>
         </is>
       </c>
     </row>
@@ -2275,23 +2275,23 @@
       </c>
       <c r="G52" s="14" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>삼현  (편출)</t>
         </is>
       </c>
       <c r="H52" s="15" t="n">
         <v>-27</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-265990500</v>
+        <v>-72292500</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>4.62%→3.89%</t>
+          <t>0.20%→0.00%</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
-          <t>168→141</t>
+          <t>27→0</t>
         </is>
       </c>
     </row>
@@ -2319,90 +2319,90 @@
       </c>
       <c r="G53" s="14" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="H53" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-56100000</v>
+        <v>-42712500</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>0.59%→0.44%</t>
+          <t>0.42%→0.30%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
-          <t>95→70</t>
+          <t>88→63</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>코스메카코리아  (신규)</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="B54" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>69785000</v>
+        <v>31025000</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.20%</t>
+          <t>0.60%→0.69%</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>0→10</t>
+          <t>69→79</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="H54" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-42712500</v>
+        <v>-56100000</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>0.42%→0.30%</t>
+          <t>0.59%→0.44%</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
         <is>
-          <t>88→63</t>
+          <t>95→70</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>코스메카코리아  (신규)</t>
         </is>
       </c>
       <c r="B55" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>31025000</v>
+        <v>69785000</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>0.60%→0.69%</t>
+          <t>0.00%→0.20%</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
-          <t>69→79</t>
+          <t>0→10</t>
         </is>
       </c>
       <c r="G55" s="14" t="inlineStr">

--- a/reports/pdf_rolling5_20260716.xlsx
+++ b/reports/pdf_rolling5_20260716.xlsx
@@ -1455,23 +1455,23 @@
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="B24" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>327672000</v>
+        <v>493279200</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>2.15%→1.74%</t>
+          <t>1.26%→1.33%</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>74→77</t>
+          <t>36→39</t>
         </is>
       </c>
       <c r="G24" s="17" t="n"/>
@@ -1483,23 +1483,23 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="B25" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>493279200</v>
+        <v>327672000</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>1.26%→1.33%</t>
+          <t>2.15%→1.74%</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>36→39</t>
+          <t>74→77</t>
         </is>
       </c>
       <c r="G25" s="17" t="n"/>
@@ -2231,23 +2231,23 @@
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>삼현  (편출)</t>
         </is>
       </c>
       <c r="H51" s="15" t="n">
         <v>-27</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-265990500</v>
+        <v>-72292500</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>4.62%→3.89%</t>
+          <t>0.20%→0.00%</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
         <is>
-          <t>168→141</t>
+          <t>27→0</t>
         </is>
       </c>
     </row>
@@ -2275,23 +2275,23 @@
       </c>
       <c r="G52" s="14" t="inlineStr">
         <is>
-          <t>삼현  (편출)</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="H52" s="15" t="n">
         <v>-27</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-72292500</v>
+        <v>-265990500</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>0.20%→0.00%</t>
+          <t>4.62%→3.89%</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
-          <t>27→0</t>
+          <t>168→141</t>
         </is>
       </c>
     </row>
@@ -2319,23 +2319,23 @@
       </c>
       <c r="G53" s="14" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="H53" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-42712500</v>
+        <v>-56100000</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>0.42%→0.30%</t>
+          <t>0.59%→0.44%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
-          <t>88→63</t>
+          <t>95→70</t>
         </is>
       </c>
     </row>
@@ -2363,23 +2363,23 @@
       </c>
       <c r="G54" s="14" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="H54" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-56100000</v>
+        <v>-42712500</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>0.59%→0.44%</t>
+          <t>0.42%→0.30%</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
         <is>
-          <t>95→70</t>
+          <t>88→63</t>
         </is>
       </c>
     </row>
